--- a/toolkit/save-workshop-agenda.xlsx
+++ b/toolkit/save-workshop-agenda.xlsx
@@ -535,7 +535,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -558,7 +557,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
@@ -676,7 +674,6 @@
       <c r="C16" s="7" t="inlineStr"/>
       <c r="D16" s="7" t="inlineStr"/>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -810,7 +807,6 @@
       <c r="C27" s="7" t="inlineStr"/>
       <c r="D27" s="7" t="inlineStr"/>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
@@ -849,7 +845,7 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>200+ raw ideas, tagged</t>
+          <t>200–400 raw ideas, tagged</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr"/>
@@ -908,7 +904,6 @@
       <c r="C36" s="7" t="inlineStr"/>
       <c r="D36" s="7" t="inlineStr"/>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
@@ -1024,15 +1019,13 @@
       <c r="C46" s="7" t="inlineStr"/>
       <c r="D46" s="7" t="inlineStr"/>
     </row>
-    <row r="47"/>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>Facilitator rules: defer judgement in Phase 3 (enforce ruthlessly) · every idea leaves the room with an owner or it dies in the room · finance validates all savings before the Day-3 presentation. Edit times and rows freely to fit your product's complexity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49"/>
+          <t>Facilitator rules: defer judgement in Phase 3, and hold to it even with senior people in the room · every idea leaves with a named owner · finance reviews the savings figures before the decision meeting, which can be a week later. Edit times and rows freely to fit your product's complexity.</t>
+        </is>
+      </c>
+    </row>
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
